--- a/product_selector_out/STM32C59x-5A3.xlsx
+++ b/product_selector_out/STM32C59x-5A3.xlsx
@@ -4257,7 +4257,7 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -14372,9 +14372,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -14437,14 +14437,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -14672,9 +14672,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14699,9 +14699,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -14764,14 +14764,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -14999,9 +14999,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16661,9 +16661,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -16726,14 +16726,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -16961,9 +16961,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17315,9 +17315,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -17380,14 +17380,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
@@ -17615,9 +17615,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17642,9 +17642,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -17707,14 +17707,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T31" s="6" t="inlineStr">
@@ -17942,9 +17942,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21233,7 +21233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21663,7 +21663,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32C5A3VG</t>
+          <t>STM32C591RG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -21678,14 +21678,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32C5A3VG</t>
+          <t>STM32C591RG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -21700,14 +21700,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32C5A3ZG</t>
+          <t>STM32C593CE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -21722,14 +21722,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32C5A3ZG</t>
+          <t>STM32C593CE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -21744,14 +21744,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32C591RG</t>
+          <t>STM32C593CG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -21773,7 +21773,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32C591RG</t>
+          <t>STM32C593CG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -21795,7 +21795,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32C593CE</t>
+          <t>STM32C591ZE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -21817,7 +21817,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32C593CE</t>
+          <t>STM32C591ZE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -21839,7 +21839,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32C593CG</t>
+          <t>STM32C591ZG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -21861,7 +21861,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32C593CG</t>
+          <t>STM32C591ZG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -21883,7 +21883,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32C591ZE</t>
+          <t>STM32C591RE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -21905,7 +21905,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32C591ZE</t>
+          <t>STM32C591RE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -21927,7 +21927,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32C591ZG</t>
+          <t>STM32C593RG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -21949,7 +21949,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32C591ZG</t>
+          <t>STM32C593RG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -21971,7 +21971,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32C5A3RG</t>
+          <t>STM32C593VE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -21986,14 +21986,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32C5A3RG</t>
+          <t>STM32C593VE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -22008,14 +22008,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32C591RE</t>
+          <t>STM32C593MG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -22037,7 +22037,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32C591RE</t>
+          <t>STM32C593MG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -22059,7 +22059,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32C5A3KG</t>
+          <t>STM32C593RE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -22074,14 +22074,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32C5A3KG</t>
+          <t>STM32C593RE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -22096,14 +22096,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32C5A3MG</t>
+          <t>STM32C593ZG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -22118,14 +22118,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32C5A3MG</t>
+          <t>STM32C593ZG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -22140,14 +22140,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32C593RG</t>
+          <t>STM32C5A3CG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -22162,14 +22162,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32C593RG</t>
+          <t>STM32C5A3CG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -22184,14 +22184,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32C593VE</t>
+          <t>STM32C593VG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -22213,7 +22213,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32C593VE</t>
+          <t>STM32C593VG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -22235,7 +22235,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32C593MG</t>
+          <t>STM32C593ZE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -22257,7 +22257,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32C593MG</t>
+          <t>STM32C593ZE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -22279,7 +22279,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32C593RE</t>
+          <t>STM32C591CE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -22301,7 +22301,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32C593RE</t>
+          <t>STM32C591CE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -22323,7 +22323,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32C593ZG</t>
+          <t>STM32C591CG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -22345,7 +22345,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32C593ZG</t>
+          <t>STM32C591CG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22359,226 +22359,6 @@
         </is>
       </c>
       <c r="D51" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32C5A3CG</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32C5A3CG</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32C593VG</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32C593VG</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32C593ZE</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32C593ZE</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32C591CE</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32C591CE</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32C591CG</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>STM32C591CG</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
         <is>
           <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32C59x-5A3.xlsx
+++ b/product_selector_out/STM32C59x-5A3.xlsx
@@ -4257,7 +4257,7 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
     </row>
@@ -14372,9 +14372,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -14437,14 +14437,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -14672,9 +14672,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -14699,9 +14699,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -14764,14 +14764,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -14999,9 +14999,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -16661,9 +16661,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -16726,14 +16726,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -16961,9 +16961,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -17315,9 +17315,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -17380,14 +17380,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
@@ -17615,9 +17615,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -17642,9 +17642,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -17707,14 +17707,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T31" s="6" t="inlineStr">
@@ -17942,9 +17942,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -21233,7 +21233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21663,7 +21663,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32C591RG</t>
+          <t>STM32C5A3VG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -21678,14 +21678,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32C591RG</t>
+          <t>STM32C5A3VG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -21700,14 +21700,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32C593CE</t>
+          <t>STM32C5A3ZG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -21722,14 +21722,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32C593CE</t>
+          <t>STM32C5A3ZG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -21744,14 +21744,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32C593CG</t>
+          <t>STM32C591RG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -21773,7 +21773,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32C593CG</t>
+          <t>STM32C591RG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -21795,7 +21795,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32C591ZE</t>
+          <t>STM32C593CE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -21817,7 +21817,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32C591ZE</t>
+          <t>STM32C593CE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -21839,7 +21839,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32C591ZG</t>
+          <t>STM32C593CG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -21861,7 +21861,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32C591ZG</t>
+          <t>STM32C593CG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -21883,7 +21883,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32C591RE</t>
+          <t>STM32C591ZE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -21905,7 +21905,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32C591RE</t>
+          <t>STM32C591ZE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -21927,7 +21927,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32C593RG</t>
+          <t>STM32C591ZG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -21949,7 +21949,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32C593RG</t>
+          <t>STM32C591ZG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -21971,7 +21971,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32C593VE</t>
+          <t>STM32C5A3RG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -21986,14 +21986,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32C593VE</t>
+          <t>STM32C5A3RG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -22008,14 +22008,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32C593MG</t>
+          <t>STM32C591RE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -22037,7 +22037,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32C593MG</t>
+          <t>STM32C591RE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -22059,7 +22059,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32C593RE</t>
+          <t>STM32C5A3KG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -22074,14 +22074,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32C593RE</t>
+          <t>STM32C5A3KG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -22096,14 +22096,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32C593ZG</t>
+          <t>STM32C5A3MG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -22118,14 +22118,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32C593ZG</t>
+          <t>STM32C5A3MG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -22140,14 +22140,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32C5A3CG</t>
+          <t>STM32C593RG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -22162,14 +22162,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32C5A3CG</t>
+          <t>STM32C593RG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -22184,14 +22184,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32C593VG</t>
+          <t>STM32C593VE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -22213,7 +22213,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32C593VG</t>
+          <t>STM32C593VE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -22235,7 +22235,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32C593ZE</t>
+          <t>STM32C593MG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -22257,7 +22257,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32C593ZE</t>
+          <t>STM32C593MG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -22279,7 +22279,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32C591CE</t>
+          <t>STM32C593RE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -22301,7 +22301,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32C591CE</t>
+          <t>STM32C593RE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -22323,7 +22323,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32C591CG</t>
+          <t>STM32C593ZG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -22345,20 +22345,240 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>STM32C593ZG</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32C5A3CG</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>STM32C5A3CG</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32C593VG</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32C593VG</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32C593ZE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32C593ZE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32C591CE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32C591CE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>STM32C591CG</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STM32C591CG</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>Timers (32-bit) typ</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32C59x-5A3.xlsx
+++ b/product_selector_out/STM32C59x-5A3.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM41"/>
+  <dimension ref="A1:BN41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.0625" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -9489,6 +9621,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -10143,6 +10285,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -10470,6 +10617,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -10797,12 +10949,17 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -10823,16 +10980,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -10845,6 +11000,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -10864,7 +11020,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -10911,7 +11069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM41"/>
+  <dimension ref="A1:BN41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10979,6 +11137,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11312,6 +11471,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -11407,6 +11571,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -11729,7 +11894,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12056,7 +12226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12383,7 +12558,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12710,7 +12890,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13037,7 +13222,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13364,7 +13554,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13691,7 +13886,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14018,7 +14218,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14345,7 +14550,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14672,7 +14882,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14999,7 +15214,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15326,7 +15546,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15653,7 +15878,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15980,7 +16210,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16307,7 +16542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16634,7 +16874,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16961,7 +17206,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17288,7 +17538,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17615,7 +17870,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17942,7 +18202,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18269,7 +18534,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18596,7 +18866,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18923,7 +19198,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19250,7 +19530,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19577,7 +19862,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19904,7 +20194,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20231,7 +20526,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20558,7 +20858,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20885,7 +21190,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21212,7 +21522,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21220,8 +21535,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
